--- a/SLK01D.xlsx
+++ b/SLK01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t/>
   </si>
@@ -58,103 +58,190 @@
     <t>KUSUKA KRP EMPING 40</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20124748</t>
+  </si>
+  <si>
+    <t>NORBET R/LAUT ORI 30</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20124748</t>
-  </si>
-  <si>
-    <t>NORBET R/LAUT ORI 30</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20124747</t>
+  </si>
+  <si>
+    <t>NORBET R/LAUT PDS 30</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20124747</t>
-  </si>
-  <si>
-    <t>NORBET R/LAUT PDS 30</t>
+    <t>20084814</t>
+  </si>
+  <si>
+    <t>MURIA SBLK STK C/MRH</t>
+  </si>
+  <si>
+    <t>20113702</t>
+  </si>
+  <si>
+    <t>MURIA POTATO PDS 100</t>
+  </si>
+  <si>
+    <t>20101355</t>
+  </si>
+  <si>
+    <t>INTRS BASRENG PDS150</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20110656</t>
+  </si>
+  <si>
+    <t>INTIRS BTAGOR PDS100</t>
+  </si>
+  <si>
+    <t>20117330</t>
+  </si>
+  <si>
+    <t>INTIRASA KRP KACA 75</t>
+  </si>
+  <si>
+    <t>RT,(E-2.5B)</t>
+  </si>
+  <si>
+    <t>20100259</t>
+  </si>
+  <si>
+    <t>QUEEN MLD JG BK PD90</t>
+  </si>
+  <si>
+    <t>20102857</t>
+  </si>
+  <si>
+    <t>IDM KUKU MACAN 75G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20091411</t>
+  </si>
+  <si>
+    <t>NIASA SALE MST KJ150</t>
+  </si>
+  <si>
+    <t>20124676</t>
+  </si>
+  <si>
+    <t>NIASA PILUS SUPER100</t>
+  </si>
+  <si>
+    <t>20091414</t>
+  </si>
+  <si>
+    <t>NIASA KRPK KRTG SBLK</t>
+  </si>
+  <si>
+    <t>20020856</t>
+  </si>
+  <si>
+    <t>PW/KARTA SP.KENCUR90</t>
+  </si>
+  <si>
+    <t>10017484</t>
+  </si>
+  <si>
+    <t>WESTON BAGELAN 100G</t>
+  </si>
+  <si>
+    <t>20028161</t>
+  </si>
+  <si>
+    <t>NIASA MAKARONI PG200</t>
+  </si>
+  <si>
+    <t>20093323</t>
+  </si>
+  <si>
+    <t>NIASA PILUS PDS150</t>
+  </si>
+  <si>
+    <t>20105253</t>
+  </si>
+  <si>
+    <t>IDM KRPK SNKG ASN100</t>
+  </si>
+  <si>
+    <t>20092456</t>
+  </si>
+  <si>
+    <t>IDM KRPK SNGKONG 100</t>
+  </si>
+  <si>
+    <t>10008170</t>
+  </si>
+  <si>
+    <t>SUZANNA CKLAT NGT 23</t>
+  </si>
+  <si>
+    <t>20112739</t>
+  </si>
+  <si>
+    <t>MAIRA CRSPY MCRON 35</t>
+  </si>
+  <si>
+    <t>20139129</t>
+  </si>
+  <si>
+    <t>MAIRA BOLU BOLU 35G</t>
+  </si>
+  <si>
+    <t>20092052</t>
+  </si>
+  <si>
+    <t>ARBIE ARMNS WFR 170G</t>
+  </si>
+  <si>
+    <t>10039027</t>
+  </si>
+  <si>
+    <t>TUNGGAL B MARIE250GR</t>
+  </si>
+  <si>
+    <t>20049706</t>
+  </si>
+  <si>
+    <t>PICNIC DODOL GRT 250</t>
+  </si>
+  <si>
+    <t>20025507</t>
+  </si>
+  <si>
+    <t>PIA 100 COKLAT 138G</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>20084814</t>
-  </si>
-  <si>
-    <t>MURIA SBLK STK C/MRH</t>
-  </si>
-  <si>
-    <t>20113702</t>
-  </si>
-  <si>
-    <t>MURIA POTATO PDS 100</t>
-  </si>
-  <si>
-    <t>20101355</t>
-  </si>
-  <si>
-    <t>INTRS BASRENG PDS150</t>
-  </si>
-  <si>
-    <t>RT,(E-3.5B)</t>
-  </si>
-  <si>
-    <t>20110656</t>
-  </si>
-  <si>
-    <t>INTIRS BTAGOR PDS100</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20117330</t>
-  </si>
-  <si>
-    <t>INTIRASA KRP KACA 75</t>
-  </si>
-  <si>
-    <t>RT,(E-2.5B)</t>
-  </si>
-  <si>
-    <t>20100259</t>
-  </si>
-  <si>
-    <t>QUEEN MLD JG BK PD90</t>
-  </si>
-  <si>
-    <t>20102857</t>
-  </si>
-  <si>
-    <t>IDM KUKU MACAN 75G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20091411</t>
-  </si>
-  <si>
-    <t>NIASA SALE MST KJ150</t>
-  </si>
-  <si>
-    <t>20124676</t>
-  </si>
-  <si>
-    <t>NIASA PILUS SUPER100</t>
-  </si>
-  <si>
-    <t>20091414</t>
-  </si>
-  <si>
-    <t>NIASA KRPK KRTG SBLK</t>
+    <t>20025508</t>
+  </si>
+  <si>
+    <t>PIA 100 KCG HJ 138G</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>20139767</t>
@@ -163,91 +250,7 @@
     <t>KACANG TLR BWNG 125G</t>
   </si>
   <si>
-    <t>20020856</t>
-  </si>
-  <si>
-    <t>PW/KARTA SP.KENCUR90</t>
-  </si>
-  <si>
-    <t>10017484</t>
-  </si>
-  <si>
-    <t>WESTON BAGELAN 100G</t>
-  </si>
-  <si>
-    <t>20028161</t>
-  </si>
-  <si>
-    <t>NIASA MAKARONI PG200</t>
-  </si>
-  <si>
-    <t>20093323</t>
-  </si>
-  <si>
-    <t>NIASA PILUS PDS150</t>
-  </si>
-  <si>
-    <t>20105253</t>
-  </si>
-  <si>
-    <t>IDM KRPK SNKG ASN100</t>
-  </si>
-  <si>
-    <t>20092456</t>
-  </si>
-  <si>
-    <t>IDM KRPK SNGKONG 100</t>
-  </si>
-  <si>
-    <t>10008170</t>
-  </si>
-  <si>
-    <t>SUZANNA CKLAT NGT 23</t>
-  </si>
-  <si>
-    <t>20112739</t>
-  </si>
-  <si>
-    <t>MAIRA CRSPY MCRON 35</t>
-  </si>
-  <si>
-    <t>20092052</t>
-  </si>
-  <si>
-    <t>ARBIE ARMNS WFR 170G</t>
-  </si>
-  <si>
-    <t>10039027</t>
-  </si>
-  <si>
-    <t>TUNGGAL B MARIE250GR</t>
-  </si>
-  <si>
-    <t>20049706</t>
-  </si>
-  <si>
-    <t>PICNIC DODOL GRT 250</t>
-  </si>
-  <si>
-    <t>20025507</t>
-  </si>
-  <si>
-    <t>PIA 100 COKLAT 138G</t>
-  </si>
-  <si>
-    <t>20025508</t>
-  </si>
-  <si>
-    <t>PIA 100 KCG HJ 138G</t>
-  </si>
-  <si>
-    <t>20139129</t>
-  </si>
-  <si>
-    <t>MAIRA BOLU BOLU 35G</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>20106148</t>
@@ -906,7 +909,7 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>20</v>
@@ -914,10 +917,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -926,18 +929,18 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -946,7 +949,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>16</v>
@@ -954,10 +957,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -969,15 +972,15 @@
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -989,15 +992,15 @@
         <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1014,10 +1017,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1026,44 +1029,44 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>8</v>
@@ -1074,16 +1077,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>11</v>
@@ -1094,159 +1097,159 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>16</v>
@@ -1254,19 +1257,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>16</v>
@@ -1274,19 +1277,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>20</v>
@@ -1303,10 +1306,10 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>20</v>
@@ -1314,36 +1317,36 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>4</v>
@@ -1354,79 +1357,79 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>20</v>
@@ -1434,19 +1437,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>20</v>
@@ -1454,19 +1457,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>12</v>
